--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T1_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>84</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,127 +72,127 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.97e+05</t>
-  </si>
-  <si>
-    <t>(77024.681)</t>
-  </si>
-  <si>
-    <t>496.348</t>
-  </si>
-  <si>
-    <t>(33.371)</t>
-  </si>
-  <si>
-    <t>3.575</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
-  </si>
-  <si>
-    <t>11.612</t>
-  </si>
-  <si>
-    <t>(1.758)</t>
-  </si>
-  <si>
-    <t>88.860</t>
-  </si>
-  <si>
-    <t>(0.443)</t>
-  </si>
-  <si>
-    <t>1.09e+06</t>
-  </si>
-  <si>
-    <t>(52629.613)</t>
-  </si>
-  <si>
-    <t>2.609</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
   </si>
   <si>
     <t>(0.119)</t>
   </si>
   <si>
-    <t>3.541</t>
-  </si>
-  <si>
-    <t>(0.416)</t>
-  </si>
-  <si>
-    <t>34.529</t>
-  </si>
-  <si>
-    <t>(3.239)</t>
-  </si>
-  <si>
-    <t>0.976</t>
-  </si>
-  <si>
-    <t>(0.017)</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>7.03e+05</t>
-  </si>
-  <si>
-    <t>(1.28e+05)</t>
-  </si>
-  <si>
-    <t>494.043</t>
-  </si>
-  <si>
-    <t>(63.947)</t>
-  </si>
-  <si>
-    <t>3.313</t>
-  </si>
-  <si>
-    <t>(0.070)</t>
-  </si>
-  <si>
-    <t>30.069</t>
-  </si>
-  <si>
-    <t>(5.159)</t>
-  </si>
-  <si>
-    <t>91.169</t>
-  </si>
-  <si>
-    <t>(0.578)</t>
-  </si>
-  <si>
-    <t>1.35e+06</t>
-  </si>
-  <si>
-    <t>(85789.889)</t>
-  </si>
-  <si>
-    <t>3.402</t>
-  </si>
-  <si>
-    <t>(0.181)</t>
-  </si>
-  <si>
-    <t>6.690</t>
-  </si>
-  <si>
-    <t>(0.756)</t>
-  </si>
-  <si>
-    <t>46.793</t>
-  </si>
-  <si>
-    <t>(4.168)</t>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>113</t>
+    <t>116</t>
+  </si>
+  <si>
+    <t>115</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.06e+05</t>
-  </si>
-  <si>
-    <t>-2.305</t>
-  </si>
-  <si>
-    <t>-0.262***</t>
-  </si>
-  <si>
-    <t>18.457***</t>
-  </si>
-  <si>
-    <t>2.309***</t>
-  </si>
-  <si>
-    <t>2.63e+05**</t>
-  </si>
-  <si>
-    <t>0.793***</t>
-  </si>
-  <si>
-    <t>3.148***</t>
-  </si>
-  <si>
-    <t>12.264**</t>
-  </si>
-  <si>
-    <t>0.024</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T1_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>85</t>
+  </si>
+  <si>
+    <t>84</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.97e+05</t>
+  </si>
+  <si>
+    <t>(77024.681)</t>
+  </si>
+  <si>
+    <t>496.348</t>
+  </si>
+  <si>
+    <t>(33.371)</t>
+  </si>
+  <si>
+    <t>3.575</t>
+  </si>
+  <si>
+    <t>(0.044)</t>
+  </si>
+  <si>
+    <t>11.612</t>
+  </si>
+  <si>
+    <t>(1.758)</t>
+  </si>
+  <si>
+    <t>88.860</t>
+  </si>
+  <si>
+    <t>(0.443)</t>
+  </si>
+  <si>
+    <t>1.09e+06</t>
+  </si>
+  <si>
+    <t>(52629.613)</t>
+  </si>
+  <si>
+    <t>2.609</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>3.541</t>
+  </si>
+  <si>
+    <t>(0.416)</t>
+  </si>
+  <si>
+    <t>34.529</t>
+  </si>
+  <si>
+    <t>(3.239)</t>
+  </si>
+  <si>
+    <t>0.976</t>
+  </si>
+  <si>
+    <t>(0.017)</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.03e+05</t>
+  </si>
+  <si>
+    <t>(1.28e+05)</t>
+  </si>
+  <si>
+    <t>494.043</t>
+  </si>
+  <si>
+    <t>(63.947)</t>
+  </si>
+  <si>
+    <t>3.313</t>
+  </si>
+  <si>
+    <t>(0.070)</t>
+  </si>
+  <si>
+    <t>30.069</t>
+  </si>
+  <si>
+    <t>(5.159)</t>
+  </si>
+  <si>
+    <t>91.169</t>
+  </si>
+  <si>
+    <t>(0.578)</t>
+  </si>
+  <si>
+    <t>1.35e+06</t>
+  </si>
+  <si>
+    <t>(85789.889)</t>
+  </si>
+  <si>
+    <t>3.402</t>
+  </si>
+  <si>
+    <t>(0.181)</t>
+  </si>
+  <si>
+    <t>6.690</t>
+  </si>
+  <si>
+    <t>(0.756)</t>
+  </si>
+  <si>
+    <t>46.793</t>
+  </si>
+  <si>
+    <t>(4.168)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>115</t>
+    <t>114</t>
+  </si>
+  <si>
+    <t>113</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.06e+05</t>
+  </si>
+  <si>
+    <t>-2.305</t>
+  </si>
+  <si>
+    <t>-0.262***</t>
+  </si>
+  <si>
+    <t>18.457***</t>
+  </si>
+  <si>
+    <t>2.309***</t>
+  </si>
+  <si>
+    <t>2.63e+05**</t>
+  </si>
+  <si>
+    <t>0.793***</t>
+  </si>
+  <si>
+    <t>3.148***</t>
+  </si>
+  <si>
+    <t>12.264**</t>
+  </si>
+  <si>
+    <t>0.024</t>
   </si>
 </sst>
 </file>
